--- a/data/trans_camb/IP2003-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP2003-Clase-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,89; 15,41</t>
+          <t>-3,49; 15,81</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-6,41; 12,97</t>
+          <t>-6,5; 11,92</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-10,11; 4,92</t>
+          <t>-11,14; 5,56</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-14,48; 2,35</t>
+          <t>-13,54; 1,61</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-8,38; 9,46</t>
+          <t>-8,47; 8,13</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-12,17; 2,72</t>
+          <t>-12,4; 3,3</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-6,08; 5,85</t>
+          <t>-6,36; 5,82</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-4,76; 8,39</t>
+          <t>-4,91; 7,52</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-9,06; 1,69</t>
+          <t>-9,15; 1,93</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-18,7; 151,63</t>
+          <t>-22,97; 159,58</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-38,11; 126,46</t>
+          <t>-36,33; 115,87</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-57,13; 54,97</t>
+          <t>-60,9; 59,53</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-74,72; 34,41</t>
+          <t>-72,31; 22,97</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-44,18; 102,36</t>
+          <t>-45,61; 73,82</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-63,13; 30,78</t>
+          <t>-65,04; 38,88</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-36,81; 51,57</t>
+          <t>-36,59; 52,87</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-27,17; 71,82</t>
+          <t>-28,16; 65,14</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-52,24; 15,56</t>
+          <t>-52,18; 20,1</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,05; 14,06</t>
+          <t>-3,9; 13,3</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-9,69; 6,18</t>
+          <t>-9,23; 6,47</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-6,43; 9,93</t>
+          <t>-7,02; 9,75</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-8,35; 6,54</t>
+          <t>-8,74; 7,37</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-10,19; 3,83</t>
+          <t>-10,63; 4,44</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-4,12; 13,81</t>
+          <t>-3,92; 12,77</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,5; 7,74</t>
+          <t>-3,49; 7,45</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-7,13; 3,44</t>
+          <t>-7,69; 3,16</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-3,28; 9,01</t>
+          <t>-2,25; 9,46</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-28,2; 185,42</t>
+          <t>-30,71; 173,19</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-59,47; 89,29</t>
+          <t>-58,67; 92,02</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-43,1; 135,19</t>
+          <t>-44,78; 135,01</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-53,91; 95,31</t>
+          <t>-58,25; 121,24</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-64,21; 59,41</t>
+          <t>-66,39; 69,74</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-31,8; 210,09</t>
+          <t>-30,27; 180,11</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-25,16; 92,87</t>
+          <t>-24,69; 87,42</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-51,84; 43,19</t>
+          <t>-54,63; 38,52</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-23,12; 107,8</t>
+          <t>-19,87; 106,07</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-5,28; 13,62</t>
+          <t>-4,86; 14,85</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-13,4; 6,04</t>
+          <t>-12,7; 7,06</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-9,76; 10,91</t>
+          <t>-9,76; 11,02</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-8,02; 9,33</t>
+          <t>-8,62; 8,54</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-13,17; 3,86</t>
+          <t>-13,24; 2,42</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-12,1; 8,3</t>
+          <t>-11,99; 9,07</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-4,37; 8,85</t>
+          <t>-3,86; 8,53</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-10,13; 2,07</t>
+          <t>-10,59; 1,6</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-8,24; 5,99</t>
+          <t>-8,9; 5,54</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-30,52; 166,57</t>
+          <t>-27,99; 204,99</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-76,32; 80,07</t>
+          <t>-72,95; 105,68</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-59,9; 144,2</t>
+          <t>-62,5; 135,36</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-44,59; 89,97</t>
+          <t>-47,52; 83,25</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-72,97; 50,25</t>
+          <t>-75,46; 30,09</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-69,3; 92,64</t>
+          <t>-71,82; 91,32</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-25,1; 84,75</t>
+          <t>-23,81; 82,49</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-62,8; 19,37</t>
+          <t>-63,94; 15,21</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-51,68; 56,32</t>
+          <t>-54,62; 50,62</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-6,87; 4,89</t>
+          <t>-6,75; 4,87</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-6,2; 5,09</t>
+          <t>-6,2; 5,44</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-4,19; 41,16</t>
+          <t>-4,37; 42,3</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-7,37; 3,3</t>
+          <t>-7,64; 3,27</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-6,95; 4,36</t>
+          <t>-6,95; 4,78</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-4,22; 10,36</t>
+          <t>-3,94; 10,6</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-5,74; 2,39</t>
+          <t>-5,3; 2,53</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-4,84; 2,93</t>
+          <t>-5,18; 3,21</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 23,75</t>
+          <t>-1,82; 21,59</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-37,29; 40,64</t>
+          <t>-38,26; 39,65</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-35,08; 42,07</t>
+          <t>-34,49; 46,3</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-25,9; 341,61</t>
+          <t>-27,93; 348,66</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-43,76; 29,24</t>
+          <t>-44,16; 31,11</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-40,33; 36,35</t>
+          <t>-39,57; 42,62</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-24,42; 85,27</t>
+          <t>-23,75; 88,25</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-34,76; 18,86</t>
+          <t>-32,25; 20,38</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-30,52; 22,38</t>
+          <t>-29,98; 25,96</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-9,12; 162,92</t>
+          <t>-11,59; 160,0</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-14,15; 3,0</t>
+          <t>-15,24; 2,4</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-18,42; -1,27</t>
+          <t>-19,4; -2,07</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-12,83; 6,85</t>
+          <t>-13,86; 7,05</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-9,03; 6,37</t>
+          <t>-8,77; 6,28</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-10,83; 4,58</t>
+          <t>-10,57; 4,67</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-10,17; 17,07</t>
+          <t>-10,77; 16,83</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-8,95; 2,63</t>
+          <t>-8,89; 2,47</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-11,98; -0,55</t>
+          <t>-12,05; -0,4</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-9,45; 9,32</t>
+          <t>-9,13; 8,59</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-46,0; 17,87</t>
+          <t>-50,54; 13,35</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-61,92; -5,37</t>
+          <t>-61,6; -7,02</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-44,73; 34,01</t>
+          <t>-47,64; 37,76</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-41,71; 44,12</t>
+          <t>-41,91; 44,85</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-50,64; 33,0</t>
+          <t>-48,52; 35,53</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-52,25; 108,95</t>
+          <t>-53,97; 115,55</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-37,36; 14,62</t>
+          <t>-36,82; 13,69</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-49,51; -2,73</t>
+          <t>-48,67; -0,13</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-39,8; 49,13</t>
+          <t>-40,2; 51,48</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-16,82; 5,0</t>
+          <t>-17,29; 5,05</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-13,76; 9,65</t>
+          <t>-12,71; 9,84</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-21,28; -3,84</t>
+          <t>-21,97; -3,07</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3,66; 20,14</t>
+          <t>3,22; 19,67</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,7; 17,32</t>
+          <t>1,67; 18,28</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-3,91; 11,74</t>
+          <t>-4,4; 10,76</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-4,08; 10,06</t>
+          <t>-3,3; 9,57</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-3,3; 11,16</t>
+          <t>-4,05; 10,25</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-11,13; 0,43</t>
+          <t>-11,24; 1,01</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-67,76; 41,17</t>
+          <t>-68,08; 38,36</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-56,41; 69,34</t>
+          <t>-51,77; 71,23</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-86,69; -18,46</t>
+          <t>-84,84; -14,72</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>27,71; 865,4</t>
+          <t>21,63; 851,0</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-9,07; 770,72</t>
+          <t>-7,27; 768,46</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-67,79; 558,16</t>
+          <t>-71,61; 394,86</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-26,65; 101,62</t>
+          <t>-22,16; 92,59</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-22,92; 110,94</t>
+          <t>-26,18; 105,92</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-69,47; 8,06</t>
+          <t>-71,68; 11,7</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-3,3; 3,66</t>
+          <t>-3,32; 3,73</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-5,73; 1,03</t>
+          <t>-5,83; 1,14</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-4,07; 12,65</t>
+          <t>-4,22; 12,35</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-3,55; 2,61</t>
+          <t>-3,43; 2,67</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-4,02; 2,12</t>
+          <t>-3,82; 2,6</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-3,15; 5,91</t>
+          <t>-3,11; 5,7</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-2,32; 2,2</t>
+          <t>-2,45; 2,16</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-3,74; 0,58</t>
+          <t>-4,18; 0,55</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-2,3; 6,78</t>
+          <t>-2,42; 6,31</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-18,0; 25,86</t>
+          <t>-18,79; 25,98</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-31,85; 7,32</t>
+          <t>-32,37; 7,62</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-23,73; 78,82</t>
+          <t>-25,05; 72,86</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-23,95; 20,38</t>
+          <t>-22,19; 22,65</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-26,67; 18,0</t>
+          <t>-25,36; 20,79</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-21,77; 44,84</t>
+          <t>-20,72; 45,46</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-14,26; 15,72</t>
+          <t>-15,55; 15,52</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-23,88; 4,17</t>
+          <t>-24,9; 4,22</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-15,18; 48,54</t>
+          <t>-15,43; 43,91</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP2003-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP2003-Clase-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,49; 15,81</t>
+          <t>-4,09; 14,03</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-6,5; 11,92</t>
+          <t>-6,8; 11,83</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-11,14; 5,56</t>
+          <t>-10,18; 4,95</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-13,54; 1,61</t>
+          <t>-15,04; 1,04</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-8,47; 8,13</t>
+          <t>-7,81; 8,59</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-12,4; 3,3</t>
+          <t>-12,7; 2,95</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-6,36; 5,82</t>
+          <t>-6,06; 6,03</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-4,91; 7,52</t>
+          <t>-5,07; 7,75</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-9,15; 1,93</t>
+          <t>-9,24; 1,85</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-22,97; 159,58</t>
+          <t>-23,48; 135,57</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-36,33; 115,87</t>
+          <t>-40,48; 120,08</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-60,9; 59,53</t>
+          <t>-59,04; 55,59</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-72,31; 22,97</t>
+          <t>-74,83; 19,1</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-45,61; 73,82</t>
+          <t>-45,61; 82,72</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-65,04; 38,88</t>
+          <t>-64,1; 30,99</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-36,59; 52,87</t>
+          <t>-37,13; 51,09</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-28,16; 65,14</t>
+          <t>-28,97; 65,65</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-52,18; 20,1</t>
+          <t>-53,26; 15,22</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,9; 13,3</t>
+          <t>-3,97; 14,36</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-9,23; 6,47</t>
+          <t>-8,9; 6,32</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-7,02; 9,75</t>
+          <t>-6,32; 10,76</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-8,74; 7,37</t>
+          <t>-7,82; 6,52</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-10,63; 4,44</t>
+          <t>-9,57; 4,72</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-3,92; 12,77</t>
+          <t>-3,76; 13,67</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,49; 7,45</t>
+          <t>-3,88; 7,93</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-7,69; 3,16</t>
+          <t>-7,11; 3,04</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-2,25; 9,46</t>
+          <t>-3,58; 9,13</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-30,71; 173,19</t>
+          <t>-27,61; 205,03</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-58,67; 92,02</t>
+          <t>-58,3; 89,23</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-44,78; 135,01</t>
+          <t>-41,73; 160,69</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-58,25; 121,24</t>
+          <t>-53,56; 93,83</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-66,39; 69,74</t>
+          <t>-64,94; 69,29</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-30,27; 180,11</t>
+          <t>-30,13; 200,65</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-24,69; 87,42</t>
+          <t>-28,22; 97,73</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-54,63; 38,52</t>
+          <t>-52,57; 40,77</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-19,87; 106,07</t>
+          <t>-24,49; 114,35</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,86; 14,85</t>
+          <t>-4,87; 14,05</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-12,7; 7,06</t>
+          <t>-12,9; 5,15</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-9,76; 11,02</t>
+          <t>-9,97; 10,67</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-8,62; 8,54</t>
+          <t>-8,52; 7,76</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-13,24; 2,42</t>
+          <t>-11,95; 4,11</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-11,99; 9,07</t>
+          <t>-11,53; 9,39</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-3,86; 8,53</t>
+          <t>-4,07; 8,65</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-10,59; 1,6</t>
+          <t>-10,34; 2,15</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-8,9; 5,54</t>
+          <t>-9,32; 6,02</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-27,99; 204,99</t>
+          <t>-31,25; 162,07</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-72,95; 105,68</t>
+          <t>-74,71; 64,01</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-62,5; 135,36</t>
+          <t>-61,77; 120,38</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-47,52; 83,25</t>
+          <t>-47,97; 77,57</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-75,46; 30,09</t>
+          <t>-69,45; 47,75</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-71,82; 91,32</t>
+          <t>-68,18; 92,69</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-23,81; 82,49</t>
+          <t>-24,3; 80,09</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-63,94; 15,21</t>
+          <t>-61,94; 24,7</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-54,62; 50,62</t>
+          <t>-55,64; 57,28</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-6,75; 4,87</t>
+          <t>-6,8; 4,91</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-6,2; 5,44</t>
+          <t>-6,89; 5,3</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-4,37; 42,3</t>
+          <t>-3,89; 37,52</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-7,64; 3,27</t>
+          <t>-7,54; 2,8</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-6,95; 4,78</t>
+          <t>-6,84; 4,74</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-3,94; 10,6</t>
+          <t>-3,95; 10,67</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-5,3; 2,53</t>
+          <t>-5,92; 2,13</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-5,18; 3,21</t>
+          <t>-5,01; 3,1</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 21,59</t>
+          <t>-1,52; 23,99</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-38,26; 39,65</t>
+          <t>-38,08; 41,97</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-34,49; 46,3</t>
+          <t>-39,41; 46,6</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-27,93; 348,66</t>
+          <t>-24,52; 309,3</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-44,16; 31,11</t>
+          <t>-44,15; 27,02</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-39,57; 42,62</t>
+          <t>-38,04; 39,99</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-23,75; 88,25</t>
+          <t>-25,59; 83,73</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-32,25; 20,38</t>
+          <t>-34,87; 16,86</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-29,98; 25,96</t>
+          <t>-30,82; 24,73</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-11,59; 160,0</t>
+          <t>-10,17; 168,45</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-15,24; 2,4</t>
+          <t>-14,89; 2,6</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-19,4; -2,07</t>
+          <t>-18,61; -1,14</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-13,86; 7,05</t>
+          <t>-13,67; 7,08</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-8,77; 6,28</t>
+          <t>-9,07; 6,33</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-10,57; 4,67</t>
+          <t>-9,57; 4,96</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-10,77; 16,83</t>
+          <t>-9,63; 23,38</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-8,89; 2,47</t>
+          <t>-9,22; 2,42</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-12,05; -0,4</t>
+          <t>-11,94; -0,6</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-9,13; 8,59</t>
+          <t>-8,87; 8,37</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-50,54; 13,35</t>
+          <t>-50,52; 13,21</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-61,6; -7,02</t>
+          <t>-60,87; -5,52</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-47,64; 37,76</t>
+          <t>-45,17; 35,85</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-41,91; 44,85</t>
+          <t>-43,09; 47,53</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-48,52; 35,53</t>
+          <t>-45,65; 38,16</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-53,97; 115,55</t>
+          <t>-50,84; 174,65</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-36,82; 13,69</t>
+          <t>-37,78; 13,78</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-48,67; -0,13</t>
+          <t>-49,39; -3,78</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-40,2; 51,48</t>
+          <t>-38,68; 46,61</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-17,29; 5,05</t>
+          <t>-17,11; 4,31</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-12,71; 9,84</t>
+          <t>-12,96; 9,64</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-21,97; -3,07</t>
+          <t>-21,57; -3,8</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3,22; 19,67</t>
+          <t>4,3; 21,09</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>1,67; 18,28</t>
+          <t>1,25; 17,93</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-4,4; 10,76</t>
+          <t>-4,0; 11,41</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-3,3; 9,57</t>
+          <t>-4,63; 9,21</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-4,05; 10,25</t>
+          <t>-3,42; 10,36</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-11,24; 1,01</t>
+          <t>-11,17; 1,2</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-68,08; 38,36</t>
+          <t>-70,42; 33,73</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-51,77; 71,23</t>
+          <t>-53,94; 64,22</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-84,84; -14,72</t>
+          <t>-85,61; -16,33</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>21,63; 851,0</t>
+          <t>23,2; 926,87</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-7,27; 768,46</t>
+          <t>-12,76; 703,09</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-71,61; 394,86</t>
+          <t>-59,78; 636,72</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-22,16; 92,59</t>
+          <t>-29,62; 98,27</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-26,18; 105,92</t>
+          <t>-23,15; 107,23</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-71,68; 11,7</t>
+          <t>-70,59; 17,49</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-3,32; 3,73</t>
+          <t>-3,14; 3,79</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-5,83; 1,14</t>
+          <t>-5,83; 0,43</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-4,22; 12,35</t>
+          <t>-3,87; 13,38</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-3,43; 2,67</t>
+          <t>-3,91; 2,37</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-3,82; 2,6</t>
+          <t>-3,85; 2,26</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-3,11; 5,7</t>
+          <t>-3,51; 5,18</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-2,45; 2,16</t>
+          <t>-2,37; 2,23</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-4,18; 0,55</t>
+          <t>-3,93; 0,62</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-2,42; 6,31</t>
+          <t>-2,58; 7,07</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-18,79; 25,98</t>
+          <t>-17,0; 26,21</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-32,37; 7,62</t>
+          <t>-32,73; 3,17</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-25,05; 72,86</t>
+          <t>-23,3; 94,38</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-22,19; 22,65</t>
+          <t>-25,74; 18,8</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-25,36; 20,79</t>
+          <t>-25,45; 18,39</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-20,72; 45,46</t>
+          <t>-23,38; 42,84</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-15,55; 15,52</t>
+          <t>-14,75; 16,12</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-24,9; 4,22</t>
+          <t>-24,71; 4,22</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-15,43; 43,91</t>
+          <t>-16,75; 50,21</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP2003-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP2003-Clase-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>-6,31</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0,15</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>-4,3</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>5,83</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>2,6</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-2,38</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-6,31</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0,15</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-4,69</t>
+          <t>-1,97</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-3,59</t>
+          <t>-3,17</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,09; 14,03</t>
+          <t>-14,48; 2,35</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-6,8; 11,83</t>
+          <t>-8,38; 9,46</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-10,18; 4,95</t>
+          <t>-11,8; 3,52</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-15,04; 1,04</t>
+          <t>-2,89; 15,41</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-7,81; 8,59</t>
+          <t>-6,41; 12,97</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-12,7; 2,95</t>
+          <t>-9,82; 5,78</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-6,06; 6,03</t>
+          <t>-6,08; 5,85</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-5,07; 7,75</t>
+          <t>-4,76; 8,39</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-9,24; 1,85</t>
+          <t>-8,53; 2,16</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>-41,75%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>1,02%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>-28,46%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>41,99%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>18,7%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-17,12%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-41,75%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>1,02%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-31,05%</t>
+          <t>-14,17%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-24,82%</t>
+          <t>-21,87%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-23,48; 135,57</t>
+          <t>-74,72; 34,41</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-40,48; 120,08</t>
+          <t>-44,18; 102,36</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-59,04; 55,59</t>
+          <t>-61,1; 38,05</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-74,83; 19,1</t>
+          <t>-18,7; 151,63</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-45,61; 82,72</t>
+          <t>-38,11; 126,46</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-64,1; 30,99</t>
+          <t>-56,04; 60,26</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-37,13; 51,09</t>
+          <t>-36,81; 51,57</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-28,97; 65,65</t>
+          <t>-27,17; 71,82</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-53,26; 15,22</t>
+          <t>-50,12; 19,31</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-0,51</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-2,44</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>3,86</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>4,9</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>-1,43</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>2,0</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-0,51</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-2,44</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4,16</t>
+          <t>1,9</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>3,08</t>
+          <t>2,86</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,97; 14,36</t>
+          <t>-8,35; 6,54</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-8,9; 6,32</t>
+          <t>-10,19; 3,83</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-6,32; 10,76</t>
+          <t>-4,45; 13,63</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-7,82; 6,52</t>
+          <t>-4,05; 14,06</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-9,57; 4,72</t>
+          <t>-9,69; 6,18</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-3,76; 13,67</t>
+          <t>-6,48; 9,91</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,88; 7,93</t>
+          <t>-3,5; 7,74</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-7,11; 3,04</t>
+          <t>-7,13; 3,44</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-3,58; 9,13</t>
+          <t>-3,49; 8,53</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-4,75%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-22,53%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>35,7%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>42,34%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>-12,31%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>17,3%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-4,75%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-22,53%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>38,38%</t>
+          <t>16,45%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>27,46%</t>
+          <t>25,57%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-27,61; 205,03</t>
+          <t>-53,91; 95,31</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-58,3; 89,23</t>
+          <t>-64,21; 59,41</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-41,73; 160,69</t>
+          <t>-34,06; 206,39</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-53,56; 93,83</t>
+          <t>-28,2; 185,42</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-64,94; 69,29</t>
+          <t>-59,47; 89,29</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-30,13; 200,65</t>
+          <t>-42,15; 139,4</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-28,22; 97,73</t>
+          <t>-25,16; 92,87</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-52,57; 40,77</t>
+          <t>-51,84; 43,19</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-24,49; 114,35</t>
+          <t>-25,02; 106,08</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-0,05</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-4,93</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>-3,24</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>4,78</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>-3,56</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-0,39</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-0,05</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-4,93</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-2,75</t>
+          <t>-0,65</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-1,76</t>
+          <t>-2,1</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,87; 14,05</t>
+          <t>-8,02; 9,33</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-12,9; 5,15</t>
+          <t>-13,17; 3,86</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-9,97; 10,67</t>
+          <t>-12,58; 8,46</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-8,52; 7,76</t>
+          <t>-5,28; 13,62</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-11,95; 4,11</t>
+          <t>-13,4; 6,04</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-11,53; 9,39</t>
+          <t>-10,01; 10,36</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-4,07; 8,65</t>
+          <t>-4,37; 8,85</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-10,34; 2,15</t>
+          <t>-10,13; 2,07</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-9,32; 6,02</t>
+          <t>-8,72; 5,38</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-0,35%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-34,72%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>-22,8%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>36,72%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>-27,34%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-2,97%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-0,35%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-34,72%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-19,37%</t>
+          <t>-4,98%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-12,81%</t>
+          <t>-15,27%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-31,25; 162,07</t>
+          <t>-44,59; 89,97</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-74,71; 64,01</t>
+          <t>-72,97; 50,25</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-61,77; 120,38</t>
+          <t>-72,42; 89,54</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-47,97; 77,57</t>
+          <t>-30,52; 166,57</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-69,45; 47,75</t>
+          <t>-76,32; 80,07</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-68,18; 92,69</t>
+          <t>-61,59; 138,05</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-24,3; 80,09</t>
+          <t>-25,1; 84,75</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-61,94; 24,7</t>
+          <t>-62,8; 19,37</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-55,64; 57,28</t>
+          <t>-55,01; 53,32</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-2,32</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-1,01</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>2,38</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>-0,91</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>-0,98</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>8,94</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-2,32</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-1,01</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,71</t>
+          <t>0,86</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>5,83</t>
+          <t>1,64</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-6,8; 4,91</t>
+          <t>-7,37; 3,3</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-6,89; 5,3</t>
+          <t>-6,95; 4,36</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,89; 37,52</t>
+          <t>-4,45; 9,65</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-7,54; 2,8</t>
+          <t>-6,87; 4,89</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-6,84; 4,74</t>
+          <t>-6,2; 5,09</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-3,95; 10,67</t>
+          <t>-5,67; 8,65</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-5,92; 2,13</t>
+          <t>-5,74; 2,39</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-5,01; 3,1</t>
+          <t>-4,84; 2,93</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,52; 23,99</t>
+          <t>-3,01; 6,83</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-16,03%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-6,99%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>16,49%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>-6,03%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>-6,46%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>58,91%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-16,03%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-6,99%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>39,36%</t>
+          <t>11,09%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-38,08; 41,97</t>
+          <t>-43,76; 29,24</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-39,41; 46,6</t>
+          <t>-40,33; 36,35</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-24,52; 309,3</t>
+          <t>-25,44; 81,47</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-44,15; 27,02</t>
+          <t>-37,29; 40,64</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-38,04; 39,99</t>
+          <t>-35,08; 42,07</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-25,59; 83,73</t>
+          <t>-31,93; 71,05</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-34,87; 16,86</t>
+          <t>-34,76; 18,86</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-30,82; 24,73</t>
+          <t>-30,52; 22,38</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-10,17; 168,45</t>
+          <t>-18,82; 52,14</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>-1,28</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-2,8</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>-1,83</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>-5,97</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>-10,1</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-3,92</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>-1,28</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>-2,8</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-0,78</t>
+          <t>-6,1</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-2,32</t>
+          <t>-3,78</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-14,89; 2,6</t>
+          <t>-9,03; 6,37</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-18,61; -1,14</t>
+          <t>-10,83; 4,58</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-13,67; 7,08</t>
+          <t>-10,7; 14,21</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-9,07; 6,33</t>
+          <t>-14,15; 3,0</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-9,57; 4,96</t>
+          <t>-18,42; -1,27</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-9,63; 23,38</t>
+          <t>-14,32; 3,78</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-9,22; 2,42</t>
+          <t>-8,95; 2,63</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-11,94; -0,6</t>
+          <t>-11,98; -0,55</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-8,87; 8,37</t>
+          <t>-10,27; 5,83</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>-7,22%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-15,87%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>-10,33%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>-23,71%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>-40,1%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-15,56%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>-7,22%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>-15,87%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-4,4%</t>
+          <t>-24,22%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-11,01%</t>
+          <t>-17,93%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-50,52; 13,21</t>
+          <t>-41,71; 44,12</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-60,87; -5,52</t>
+          <t>-50,64; 33,0</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-45,17; 35,85</t>
+          <t>-55,86; 95,04</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-43,09; 47,53</t>
+          <t>-46,0; 17,87</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-45,65; 38,16</t>
+          <t>-61,92; -5,37</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-50,84; 174,65</t>
+          <t>-50,53; 18,29</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-37,78; 13,78</t>
+          <t>-37,36; 14,62</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-49,39; -3,78</t>
+          <t>-49,51; -2,73</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-38,68; 46,61</t>
+          <t>-43,54; 33,14</t>
         </is>
       </c>
     </row>
@@ -1704,32 +1704,32 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>11,94</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>9,0</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>2,48</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
           <t>-6,29</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>-2,16</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>-12,52</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>11,94</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>9,0</t>
-        </is>
-      </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,76</t>
+          <t>-12,47</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-5,18</t>
+          <t>-5,31</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-17,11; 4,31</t>
+          <t>3,66; 20,14</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-12,96; 9,64</t>
+          <t>0,7; 17,32</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-21,57; -3,8</t>
+          <t>-4,48; 10,83</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>4,3; 21,09</t>
+          <t>-16,82; 5,0</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>1,25; 17,93</t>
+          <t>-13,76; 9,65</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-4,0; 11,41</t>
+          <t>-21,45; -3,96</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-4,63; 9,21</t>
+          <t>-4,08; 10,06</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-3,42; 10,36</t>
+          <t>-3,3; 11,16</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-11,17; 1,2</t>
+          <t>-11,0; 0,19</t>
         </is>
       </c>
     </row>
@@ -1810,32 +1810,32 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>236,31%</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>178,17%</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>49,13%</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>-32,19%</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>-11,06%</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>-64,05%</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>236,31%</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>178,17%</t>
-        </is>
-      </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>54,62%</t>
+          <t>-63,79%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-41,12%</t>
+          <t>-42,09%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-70,42; 33,73</t>
+          <t>27,71; 865,4</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-53,94; 64,22</t>
+          <t>-9,07; 770,72</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-85,61; -16,33</t>
+          <t>-68,94; 529,57</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>23,2; 926,87</t>
+          <t>-67,76; 41,17</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-12,76; 703,09</t>
+          <t>-56,41; 69,34</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-59,78; 636,72</t>
+          <t>-86,61; -16,81</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-29,62; 98,27</t>
+          <t>-26,65; 101,62</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-23,15; 107,23</t>
+          <t>-22,92; 110,94</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-70,59; 17,49</t>
+          <t>-70,1; 5,42</t>
         </is>
       </c>
     </row>
@@ -1920,32 +1920,32 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>-0,64</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>-0,9</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>0,15</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>0,33</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>-2,54</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>0,92</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>-0,64</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>-0,9</t>
-        </is>
-      </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,49</t>
+          <t>-2,23</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>0,66</t>
+          <t>-1,0</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-3,14; 3,79</t>
+          <t>-3,55; 2,61</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-5,83; 0,43</t>
+          <t>-4,02; 2,12</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-3,87; 13,38</t>
+          <t>-3,29; 5,19</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-3,91; 2,37</t>
+          <t>-3,3; 3,66</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-3,85; 2,26</t>
+          <t>-5,73; 1,03</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-3,51; 5,18</t>
+          <t>-5,73; 1,16</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-2,37; 2,23</t>
+          <t>-2,32; 2,2</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-3,93; 0,62</t>
+          <t>-3,74; 0,58</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-2,58; 7,07</t>
+          <t>-3,3; 2,14</t>
         </is>
       </c>
     </row>
@@ -2026,32 +2026,32 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>-4,67%</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>-6,58%</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>1,09%</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
           <t>1,99%</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>-15,47%</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>5,62%</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>-4,67%</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>-6,58%</t>
-        </is>
-      </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>-13,59%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>-6,68%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-17,0; 26,21</t>
+          <t>-23,95; 20,38</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-32,73; 3,17</t>
+          <t>-26,67; 18,0</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-23,3; 94,38</t>
+          <t>-22,73; 41,49</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-25,74; 18,8</t>
+          <t>-18,0; 25,86</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-25,45; 18,39</t>
+          <t>-31,85; 7,32</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-23,38; 42,84</t>
+          <t>-31,95; 9,28</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-14,75; 16,12</t>
+          <t>-14,26; 15,72</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-24,71; 4,22</t>
+          <t>-23,88; 4,17</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-16,75; 50,21</t>
+          <t>-21,0; 15,01</t>
         </is>
       </c>
     </row>
